--- a/output/wline_비교.xlsx
+++ b/output/wline_비교.xlsx
@@ -780,7 +780,7 @@
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>가히 멀티밤 리필키트 (9g) 2개</t>
+          <t>멀티밤 리필키트 (9g) 2개</t>
         </is>
       </c>
       <c r="G11" s="4" t="n"/>
